--- a/data/missile_attacks_clean.xlsx
+++ b/data/missile_attacks_clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/berg/Core/Job/WarTracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E448C8-6DA8-6F48-A67B-5F0FDBACDECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9726CD-1139-6E41-A860-10541A5A6FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6515" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6518" uniqueCount="81">
   <si>
     <t>date</t>
   </si>
@@ -274,6 +274,9 @@
   <si>
     <t>X-101/Iskander-K and Kaliber</t>
   </si>
+  <si>
+    <t>Medium-range ballistic missile</t>
+  </si>
 </sst>
 </file>
 
@@ -282,7 +285,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -295,6 +298,19 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -325,7 +341,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -413,12 +429,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -474,6 +514,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -55685,12 +55729,27 @@
       <c r="H2170" s="17"/>
     </row>
     <row r="2171" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2171" s="9"/>
-      <c r="E2171" s="22"/>
-      <c r="F2171" s="20"/>
-      <c r="G2171" s="7" t="e">
-        <f>Table1[[#This Row],[destroyed]]/Table1[[#This Row],[launched]]</f>
-        <v>#DIV/0!</v>
+      <c r="A2171" s="9">
+        <v>46166</v>
+      </c>
+      <c r="B2171" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2171" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2171" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2171" s="22">
+        <v>1</v>
+      </c>
+      <c r="F2171" s="20">
+        <v>0</v>
+      </c>
+      <c r="G2171" s="7">
+        <f>Table1[[#This Row],[destroyed]]/Table1[[#This Row],[launched]]</f>
+        <v>0</v>
       </c>
       <c r="H2171" s="17"/>
     </row>
